--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -723,22 +723,22 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -771,12 +771,12 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -937,7 +937,895 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +804,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1187,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1220,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1244,17 +1280,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1264,13 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1298,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1331,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1355,17 +1399,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1375,13 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1819,13 +1867,584 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>—/9</t>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,18 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1114,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1229,24 +1233,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1352,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1461,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1490,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1522,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1580,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1601,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1641,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1699,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -1712,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1736,33 +1760,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1862,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1877,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1905,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1938,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1962,37 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2103,7 +2135,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2203,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2218,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2329,7 +2361,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2439,12 +2471,1265 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2278,32 +2278,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2335,33 +2339,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2389,32 +2397,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2422,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2446,17 +2458,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2466,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2504,32 +2516,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -2537,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,33 +2577,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2702,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2802,7 +2822,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2874,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2913,7 +2933,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2985,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3024,7 +3044,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3039,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3139,7 +3159,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3154,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3269,7 +3289,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3384,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,7 +3580,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3614,7 +3634,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3695,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3729,7 +3749,915 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2750,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>08:41</t>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2807,17 +2811,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2827,13 +2831,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,32 +2980,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3005,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3029,17 +3041,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3049,17 +3061,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3087,32 +3099,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3120,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3144,17 +3160,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3164,12 +3180,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3202,32 +3218,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3235,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3259,17 +3279,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3279,17 +3299,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3317,32 +3337,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3350,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3374,37 +3398,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,7 +3528,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3580,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3634,7 +3658,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3734,7 +3758,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3749,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3849,7 +3873,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3925,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3964,7 +3988,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4036,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4190,7 +4214,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4266,7 +4290,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4421,12 +4445,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4492,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4536,13 +4560,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4550,22 +4578,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4598,12 +4626,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4617,47 +4645,733 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>85.5</t>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,14 +2473,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>85.5</t>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,18 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,7 +3060,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3071,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3180,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3428,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,17 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3801,32 +3805,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -3834,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3858,17 +3866,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3878,17 +3886,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3999,7 +4007,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -4027,32 +4035,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4060,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4084,17 +4096,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4104,17 +4116,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4142,32 +4154,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -4175,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4199,17 +4215,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4219,7 +4235,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4229,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4257,32 +4273,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -4290,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4314,33 +4334,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4392,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4401,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4425,17 +4453,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4445,17 +4473,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4555,7 +4583,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4570,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4598,32 +4626,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -4631,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4655,17 +4687,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4675,17 +4707,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4785,7 +4817,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4800,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4915,7 +4947,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4976,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5026,7 +5058,7 @@
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5119,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5126,7 +5158,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5141,7 +5173,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5234,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5246,7 +5278,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5256,7 +5288,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5349,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5361,17 +5393,703 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>1/14</t>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,13 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2488,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2945,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3021,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,7 +3302,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3608,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3723,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3842,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3957,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,13 +4005,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,17 +4243,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,7 +4357,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4429,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4544,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4656,12 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4663,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4778,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4893,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,32 +4983,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -5008,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,17 +5044,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5052,13 +5064,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5201,32 +5217,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -5234,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5258,17 +5278,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5278,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5388,7 +5408,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5431,32 +5451,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:41</t>
@@ -5464,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5488,17 +5512,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5508,17 +5532,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5618,7 +5642,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5694,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,7 +5833,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5848,7 +5872,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5920,7 +5944,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6089,7 +6113,578 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,22 +3064,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4825,22 +4825,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,22 +5174,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,24 +5461,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5685,32 +5685,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5718,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5742,37 +5746,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5800,32 +5804,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -5833,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5857,17 +5865,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5877,13 +5885,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5911,32 +5923,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5944,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5968,37 +5984,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6098,7 +6114,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6174,7 +6190,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,7 +6305,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6343,7 +6359,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6420,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,7 +6535,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6573,7 +6589,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6650,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6678,13 +6694,477 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>86.7</t>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,22 +3302,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,14 +4238,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>86.7</t>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,14 +5293,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>86.7</t>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5408,22 +5408,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5933,24 +5933,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6042,32 +6042,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6075,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6099,17 +6103,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6119,17 +6123,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6157,32 +6161,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -6190,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6214,37 +6222,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6272,32 +6280,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6305,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6329,37 +6341,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6502,32 +6514,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6535,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6559,37 +6575,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6704,7 +6720,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6781,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6804,7 +6820,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6819,7 +6835,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6896,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6919,7 +6935,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6934,7 +6950,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6995,7 +7011,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7039,17 +7055,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7126,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7159,10 +7175,930 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
         <is>
           <t>11/15</t>
         </is>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4830,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,22 +5174,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5766,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5880,22 +5880,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5999,22 +5999,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,17 +6123,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6633,32 +6633,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -6666,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6690,37 +6694,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6748,32 +6752,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6781,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6805,17 +6813,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6825,7 +6833,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6835,7 +6843,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6863,32 +6871,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6896,7 +6908,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6920,17 +6932,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6940,17 +6952,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6978,32 +6990,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7011,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7035,17 +7051,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7055,17 +7071,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7093,32 +7109,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7126,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7150,37 +7170,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7280,7 +7300,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7295,7 +7315,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7323,32 +7343,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7356,7 +7380,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7380,17 +7404,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7400,17 +7424,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7495,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,7 +7610,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7640,7 +7664,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7725,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7816,7 +7840,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7878,22 +7902,22 @@
       <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -7926,12 +7950,12 @@
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7975,17 +7999,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7993,7 +8017,7 @@
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -8003,7 +8027,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -8041,12 +8065,12 @@
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8060,47 +8084,852 @@
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W65" s="2" t="inlineStr">
+      <c r="W67" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X65" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z65" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>88.3</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>11/15</t>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7131,12 +7131,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8933,6 +8933,236 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,22 +3302,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,22 +4119,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,22 +4357,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5408,22 +5408,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5642,22 +5642,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6237,22 +6237,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6471,22 +6471,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6590,22 +6590,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6828,22 +6828,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7000,24 +7000,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7228,32 +7228,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -7261,7 +7265,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7285,17 +7289,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7305,12 +7309,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7353,24 +7357,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7380,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7419,7 +7423,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7429,7 +7433,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7462,32 +7466,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -7495,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7519,17 +7527,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7539,17 +7547,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7577,32 +7585,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -7610,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7634,37 +7646,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7692,32 +7704,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7725,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7749,37 +7765,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7807,32 +7823,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7840,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7864,37 +7884,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7922,32 +7942,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -7955,7 +7979,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7979,37 +8003,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8037,32 +8061,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8070,7 +8098,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8094,37 +8122,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8224,7 +8252,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8300,7 +8328,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8339,7 +8367,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8354,7 +8382,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8443,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8454,7 +8482,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8530,7 +8558,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8645,7 +8673,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8760,7 +8788,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8875,7 +8903,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8919,12 +8947,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -8990,7 +9018,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9039,12 +9067,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9133,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9149,17 +9177,1052 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>8/15</t>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,17 +2239,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,17 +3651,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,22 +4000,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,22 +4476,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4940,22 +4940,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5059,22 +5059,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,22 +5293,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6118,17 +6118,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6356,17 +6356,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7066,17 +7066,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7304,22 +7304,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7423,17 +7423,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7542,22 +7542,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8640,32 +8640,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8673,7 +8677,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8697,37 +8701,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8755,32 +8759,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8788,7 +8796,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8812,37 +8820,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8870,32 +8878,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -8903,7 +8915,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8927,37 +8939,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8985,32 +8997,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9018,7 +9034,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9042,32 +9058,32 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9100,32 +9116,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -9133,7 +9153,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9157,37 +9177,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9268,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9287,7 +9307,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9330,32 +9350,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9363,7 +9387,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9387,32 +9411,32 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9478,7 +9502,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9532,7 +9556,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9617,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9632,7 +9656,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9708,7 +9732,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9823,7 +9847,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9938,7 +9962,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10053,7 +10077,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10168,7 +10192,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10226,6 +10250,1041 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,17 +3890,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,22 +4000,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4830,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4940,22 +4940,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5059,22 +5059,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5766,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6242,17 +6242,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6828,22 +6828,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6952,17 +6952,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7304,22 +7304,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7666,17 +7666,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8137,22 +8137,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8372,17 +8372,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8487,17 +8487,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8716,22 +8716,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8954,22 +8954,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9235,32 +9235,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -9268,7 +9272,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9292,17 +9296,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9312,17 +9316,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9360,12 +9364,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -9387,7 +9391,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9436,12 +9440,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9506,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9541,7 +9545,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9556,7 +9560,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9584,32 +9588,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9617,7 +9625,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9641,17 +9649,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9661,12 +9669,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9732,7 +9740,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9771,7 +9779,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9814,32 +9822,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>08:41</t>
@@ -9847,7 +9859,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9871,17 +9883,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9891,12 +9903,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9929,32 +9941,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9962,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9986,37 +10002,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10044,32 +10060,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -10077,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10101,17 +10121,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10121,17 +10141,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10159,32 +10179,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10192,7 +10216,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10216,17 +10240,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10236,17 +10260,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10274,32 +10298,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10307,7 +10335,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10331,37 +10359,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10450,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10476,7 +10504,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10565,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10576,7 +10604,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10591,7 +10619,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10619,32 +10647,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -10652,7 +10684,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10676,37 +10708,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10799,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10821,7 +10853,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10914,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10921,7 +10953,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -10997,7 +11029,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11046,12 +11078,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11144,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11156,17 +11188,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11174,22 +11206,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11222,12 +11254,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11271,17 +11303,822 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB92" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>13/15</t>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,17 +3890,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,17 +4124,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,17 +6123,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6242,17 +6242,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6833,17 +6833,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7071,17 +7071,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7428,17 +7428,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7547,17 +7547,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7666,17 +7666,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7904,17 +7904,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8142,17 +8142,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8840,17 +8840,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9197,17 +9197,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9316,17 +9316,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9435,17 +9435,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10022,17 +10022,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10532,32 +10532,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10565,7 +10569,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10589,17 +10593,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10609,17 +10613,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10688,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10738,7 +10742,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -10766,32 +10770,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10799,7 +10807,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10823,17 +10831,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10843,17 +10851,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10881,32 +10889,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -10914,7 +10926,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10938,17 +10950,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10958,17 +10970,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10996,32 +11008,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11029,7 +11045,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11053,17 +11069,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11073,17 +11089,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11111,32 +11127,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -11144,7 +11164,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11168,17 +11188,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11188,17 +11208,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11226,32 +11246,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11259,7 +11283,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11283,17 +11307,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11303,17 +11327,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11341,32 +11365,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11374,7 +11402,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11398,17 +11426,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11418,7 +11446,7 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
@@ -11428,7 +11456,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11517,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11543,7 +11571,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11632,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11658,7 +11686,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11747,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11763,17 +11791,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -11801,32 +11829,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11834,7 +11866,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11858,17 +11890,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11878,17 +11910,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11896,22 +11928,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11944,12 +11976,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11963,7 +11995,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -11993,17 +12025,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -12011,22 +12043,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12059,12 +12091,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12078,47 +12110,507 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>85.8</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>8/15</t>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,17 +5532,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5647,17 +5647,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,17 +6476,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7547,17 +7547,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8023,17 +8023,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8257,17 +8257,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8487,17 +8487,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9197,17 +9197,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9784,17 +9784,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9903,17 +9903,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10141,17 +10141,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10970,17 +10970,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11256,24 +11256,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11484,32 +11484,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -11517,7 +11521,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11541,17 +11545,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11561,17 +11565,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11805,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -11839,24 +11843,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11866,7 +11870,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11915,12 +11919,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11948,32 +11952,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:41</t>
@@ -11981,7 +11989,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12005,17 +12013,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12025,17 +12033,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -12063,32 +12071,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -12096,7 +12108,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12120,17 +12132,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12140,17 +12152,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12211,7 +12223,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12265,7 +12277,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12293,32 +12305,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -12326,7 +12342,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12350,17 +12366,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12370,17 +12386,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -12441,7 +12457,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12485,17 +12501,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12572,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12600,17 +12616,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东78路.xlsx
+++ b/data/export/2026-10-31-浦东78路.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10975,12 +10975,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12315,24 +12315,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -12424,32 +12424,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>08:41</t>
@@ -12457,7 +12461,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12481,17 +12485,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12501,12 +12505,12 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12572,7 +12576,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
